--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="274">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -645,6 +645,9 @@
   </si>
   <si>
     <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>image/png</t>
   </si>
   <si>
     <t>text/plain; charset=UTF-8, image/png</t>
@@ -5345,10 +5348,10 @@
         <v>21</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>21</v>
@@ -5360,13 +5363,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -5384,7 +5387,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5399,18 +5402,18 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5436,14 +5439,14 @@
         <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -5456,7 +5459,7 @@
         <v>21</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>21</v>
@@ -5492,7 +5495,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5510,15 +5513,15 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5541,19 +5544,19 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -5602,7 +5605,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5617,18 +5620,18 @@
         <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5651,19 +5654,19 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -5676,7 +5679,7 @@
         <v>21</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>21</v>
@@ -5712,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5727,18 +5730,18 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5761,19 +5764,19 @@
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -5822,7 +5825,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -5840,15 +5843,15 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5871,19 +5874,19 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -5932,7 +5935,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5950,15 +5953,15 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5984,14 +5987,14 @@
         <v>121</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6004,7 +6007,7 @@
         <v>21</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>21</v>
@@ -6040,7 +6043,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6058,15 +6061,15 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6089,17 +6092,17 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -6148,7 +6151,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6166,12 +6169,12 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>145</v>
@@ -6279,7 +6282,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>150</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-groupidentifier-create.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
